--- a/artfynd/A 40600-2023 artfynd.xlsx
+++ b/artfynd/A 40600-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124102992</v>
+        <v>131417774</v>
       </c>
       <c r="B2" t="n">
-        <v>56482</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,46 +686,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100088</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Torvsjön, dike vid stig, Hl</t>
+          <t>Torvsjön, Hl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>379086</v>
+        <v>379130</v>
       </c>
       <c r="R2" t="n">
-        <v>6286895</v>
+        <v>6286930</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,12 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,15 +765,443 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>August Oljeqvist</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>August Oljeqvist, Jonas Göransson, Amanda Rudelius</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>124102992</v>
+      </c>
+      <c r="B3" t="n">
+        <v>56895</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100088</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vanlig snok</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Natrix natrix</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Torvsjön, dike vid stig, Hl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>379086</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6286895</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Snöstorp</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Lars Stibe</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Lars Stibe</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>61741181</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Halmstad, Torvsjön, Hl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>378865</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6286877</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Snöstorp</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2016-10-09</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2016-10-09</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Börje Andersson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Börje Andersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>62160401</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Halmstad, Torvsjön, Hl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>378945</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6286785</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Snöstorp</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2016-11-20</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2016-11-20</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Börje Andersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Börje Andersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>130053968</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Halmstad, Torvsjön, Hl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>378855</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6286902</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Halmstad</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Snöstorp</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-08</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Börje Andersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Börje Andersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40600-2023 artfynd.xlsx
+++ b/artfynd/A 40600-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131417774</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,6 +891,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124102992</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -988,6 +1003,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61741181</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1095,6 +1115,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62160401</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,8 +1227,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130053968</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>